--- a/backend/app/templates/postal_region_template.xlsx
+++ b/backend/app/templates/postal_region_template.xlsx
@@ -571,7 +571,7 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -687,6 +687,16 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0"/>
@@ -1029,7 +1039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="9" customWidth="1" style="8" min="1" max="2"/>
@@ -1121,7 +1131,23 @@
         </is>
       </c>
     </row>
-    <row r="2" customFormat="1" s="5"/>
+    <row r="2" customFormat="1" s="5">
+      <c r="A2" s="43" t="n"/>
+      <c r="B2" s="43" t="n"/>
+      <c r="C2" s="43" t="n"/>
+      <c r="D2" s="43" t="n"/>
+      <c r="E2" s="33" t="n"/>
+      <c r="F2" s="33" t="n"/>
+      <c r="G2" s="33" t="n"/>
+      <c r="H2" s="44" t="n"/>
+      <c r="I2" s="45" t="n"/>
+      <c r="J2" s="36" t="n"/>
+      <c r="K2" s="36" t="n"/>
+      <c r="L2" s="36" t="n"/>
+      <c r="M2" s="36" t="n"/>
+      <c r="N2" s="46" t="n"/>
+      <c r="O2" s="36" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
